--- a/Generators/Experiment with utility data leak/utility results/9. MAGIC Gamma Telescope/TRTR_TSTR_results_merged.xlsx
+++ b/Generators/Experiment with utility data leak/utility results/9. MAGIC Gamma Telescope/TRTR_TSTR_results_merged.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="TRTR_Results" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="All_Comparisons" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Summary" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="CTGAN" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="CopulaGAN" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="TVAE" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="GaussianCopula" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="WGAN_GP" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="CTABGAN" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="TabDDPM" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="ForestDiffusion" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TRTR_Results" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="All_Comparisons" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CTGAN" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CopulaGAN" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TVAE" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GaussianCopula" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WGAN_GP" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CTABGAN" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TabDDPM" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ForestDiffusion" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -27,13 +27,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -44,7 +47,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -52,12 +55,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -427,67 +439,67 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Model</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Accuracy Mean</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Accuracy Std</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>F1 Mean</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>F1 Std</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Precision Mean</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Precision Std</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Recall Mean</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Recall Std</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Accuracy (Mean±Std)</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>F1 (Mean±Std)</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Precision (Mean±Std)</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Recall (Mean±Std)</t>
         </is>
@@ -1018,152 +1030,152 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Model</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Accuracy Mean_TRTR</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Accuracy Std_TRTR</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>F1 Mean_TRTR</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>F1 Std_TRTR</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Precision Mean_TRTR</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Precision Std_TRTR</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Recall Mean_TRTR</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Recall Std_TRTR</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Accuracy (Mean±Std)_TRTR</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>F1 (Mean±Std)_TRTR</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Precision (Mean±Std)_TRTR</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Recall (Mean±Std)_TRTR</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Accuracy Mean_TSTR</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Accuracy Std_TSTR</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>F1 Mean_TSTR</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>F1 Std_TSTR</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Precision Mean_TSTR</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Precision Std_TSTR</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Recall Mean_TSTR</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Recall Std_TSTR</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Accuracy (Mean±Std)_TSTR</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>F1 (Mean±Std)_TSTR</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Precision (Mean±Std)_TSTR</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Recall (Mean±Std)_TSTR</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>Accuracy_Drop</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>F1_Drop</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>Precision_Drop</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>Recall_Drop</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>Synthetic_Model</t>
         </is>
@@ -1220,60 +1232,60 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>0.6348580441640378</v>
+        <v>0.6350157728706625</v>
       </c>
       <c r="O2" t="n">
-        <v>0.007403734637461534</v>
+        <v>0.01100728412878248</v>
       </c>
       <c r="P2" t="n">
-        <v>0.7667000074249125</v>
+        <v>0.7603254543816355</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.005034609332349129</v>
+        <v>0.008034252722485523</v>
       </c>
       <c r="R2" t="n">
-        <v>0.6544041973465721</v>
+        <v>0.6619125822373438</v>
       </c>
       <c r="S2" t="n">
-        <v>0.004338417108145803</v>
+        <v>0.005858886471172387</v>
       </c>
       <c r="T2" t="n">
-        <v>0.9255879967558801</v>
+        <v>0.8931873479318735</v>
       </c>
       <c r="U2" t="n">
-        <v>0.009997815966181945</v>
+        <v>0.01386861313868614</v>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>0.6349 ± 0.0074</t>
+          <t>0.6350 ± 0.0110</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>0.7667 ± 0.0050</t>
+          <t>0.7603 ± 0.0080</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>0.6544 ± 0.0043</t>
+          <t>0.6619 ± 0.0059</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>0.9256 ± 0.0100</t>
+          <t>0.8932 ± 0.0139</t>
         </is>
       </c>
       <c r="Z2" t="n">
-        <v>0.2454784437434279</v>
+        <v>0.2453207150368032</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.1439488457518913</v>
+        <v>0.1503233987951683</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.2280846643005098</v>
+        <v>0.220576279409738</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.01508515815085143</v>
+        <v>0.04748580697485805</v>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
@@ -1332,60 +1344,60 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0.6383280757097791</v>
+        <v>0.6346740273396425</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0109225784870775</v>
+        <v>0.01333046061162599</v>
       </c>
       <c r="P3" t="n">
-        <v>0.7683501460435098</v>
+        <v>0.7597423295254266</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.006850936582404506</v>
+        <v>0.008993136587323919</v>
       </c>
       <c r="R3" t="n">
-        <v>0.6569913439502555</v>
+        <v>0.6621770093572454</v>
       </c>
       <c r="S3" t="n">
-        <v>0.006793804218780486</v>
+        <v>0.007696943175684294</v>
       </c>
       <c r="T3" t="n">
-        <v>0.9252635847526356</v>
+        <v>0.8910786699107867</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0112760153608929</v>
+        <v>0.01278781133215969</v>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>0.6383 ± 0.0109</t>
+          <t>0.6347 ± 0.0133</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>0.7684 ± 0.0069</t>
+          <t>0.7597 ± 0.0090</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.6570 ± 0.0068</t>
+          <t>0.6622 ± 0.0077</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>0.9253 ± 0.0113</t>
+          <t>0.8911 ± 0.0128</t>
         </is>
       </c>
       <c r="Z3" t="n">
-        <v>0.2400105152471084</v>
+        <v>0.243664563617245</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.1416865634162571</v>
+        <v>0.1502943799343402</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.217012055597525</v>
+        <v>0.2118263901905351</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.02392538523925403</v>
+        <v>0.05811030008110296</v>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
@@ -1444,60 +1456,60 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>0.6310988433228182</v>
+        <v>0.662565720294427</v>
       </c>
       <c r="O4" t="n">
-        <v>0.01057099444446813</v>
+        <v>0.0169301193155502</v>
       </c>
       <c r="P4" t="n">
-        <v>0.7517808777331801</v>
+        <v>0.7682960618487664</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.008808504610388224</v>
+        <v>0.01267884580834273</v>
       </c>
       <c r="R4" t="n">
-        <v>0.6666927638610544</v>
+        <v>0.6922262985485927</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0070720508501763</v>
+        <v>0.00974024592714598</v>
       </c>
       <c r="T4" t="n">
-        <v>0.8621654501216545</v>
+        <v>0.8633008921330088</v>
       </c>
       <c r="U4" t="n">
-        <v>0.02189289091961426</v>
+        <v>0.02004118167164525</v>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>0.6311 ± 0.0106</t>
+          <t>0.6626 ± 0.0169</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>0.7518 ± 0.0088</t>
+          <t>0.7683 ± 0.0127</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>0.6667 ± 0.0071</t>
+          <t>0.6922 ± 0.0097</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>0.8622 ± 0.0219</t>
+          <t>0.8633 ± 0.0200</t>
         </is>
       </c>
       <c r="Z4" t="n">
-        <v>0.2468980021030491</v>
+        <v>0.2154311251314404</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.1570949489768096</v>
+        <v>0.1405797648612234</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.2143390609425785</v>
+        <v>0.1888055262550401</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.07643957826439596</v>
+        <v>0.07530413625304166</v>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
@@ -1556,60 +1568,60 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>0.6281808622502629</v>
+        <v>0.629074658254469</v>
       </c>
       <c r="O5" t="n">
-        <v>0.008438608645194129</v>
+        <v>0.00972091799610684</v>
       </c>
       <c r="P5" t="n">
-        <v>0.7578194488136557</v>
+        <v>0.75329248607062</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.005639916438486107</v>
+        <v>0.007593777351620037</v>
       </c>
       <c r="R5" t="n">
-        <v>0.6558601421759096</v>
+        <v>0.6621154684467924</v>
       </c>
       <c r="S5" t="n">
-        <v>0.005674490808419633</v>
+        <v>0.005626386807195845</v>
       </c>
       <c r="T5" t="n">
-        <v>0.8974452554744528</v>
+        <v>0.8737631792376318</v>
       </c>
       <c r="U5" t="n">
-        <v>0.01186774144616095</v>
+        <v>0.01600942216071113</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>0.6282 ± 0.0084</t>
+          <t>0.6291 ± 0.0097</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.7578 ± 0.0056</t>
+          <t>0.7533 ± 0.0076</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.6559 ± 0.0057</t>
+          <t>0.6621 ± 0.0056</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>0.8974 ± 0.0119</t>
+          <t>0.8738 ± 0.0160</t>
         </is>
       </c>
       <c r="Z5" t="n">
-        <v>0.243322818086225</v>
+        <v>0.242429022082019</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.1476271173693666</v>
+        <v>0.1521540801124023</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.2098416763533193</v>
+        <v>0.2035863500824365</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.05158150851581489</v>
+        <v>0.07526358475263584</v>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
@@ -1668,60 +1680,60 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>0.6043638275499473</v>
+        <v>0.6023396424815983</v>
       </c>
       <c r="O6" t="n">
-        <v>0.01003297302396089</v>
+        <v>0.01224306820402052</v>
       </c>
       <c r="P6" t="n">
-        <v>0.724332197313248</v>
+        <v>0.7153860210376379</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.007641871099014639</v>
+        <v>0.009801680407231356</v>
       </c>
       <c r="R6" t="n">
-        <v>0.660512122828971</v>
+        <v>0.667250789080277</v>
       </c>
       <c r="S6" t="n">
-        <v>0.006529411639070338</v>
+        <v>0.007553444844003219</v>
       </c>
       <c r="T6" t="n">
-        <v>0.8019059205190592</v>
+        <v>0.7710867802108679</v>
       </c>
       <c r="U6" t="n">
-        <v>0.01278401727314183</v>
+        <v>0.01463819297059818</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>0.6044 ± 0.0100</t>
+          <t>0.6023 ± 0.0122</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.7243 ± 0.0076</t>
+          <t>0.7154 ± 0.0098</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>0.6605 ± 0.0065</t>
+          <t>0.6673 ± 0.0076</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>0.8019 ± 0.0128</t>
+          <t>0.7711 ± 0.0146</t>
         </is>
       </c>
       <c r="Z6" t="n">
-        <v>0.2335436382754995</v>
+        <v>0.2355678233438485</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.1582919445598115</v>
+        <v>0.1672381208354217</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.1712654339740611</v>
+        <v>0.1645267677227551</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.1381995133819952</v>
+        <v>0.1690186536901865</v>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
@@ -1780,60 +1792,60 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>0.6452944269190326</v>
+        <v>0.6441377497371187</v>
       </c>
       <c r="O7" t="n">
-        <v>0.005906408310205905</v>
+        <v>0.007461427371196214</v>
       </c>
       <c r="P7" t="n">
-        <v>0.7820984572517805</v>
+        <v>0.7742831695281365</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.004544786967065663</v>
+        <v>0.007054059690694768</v>
       </c>
       <c r="R7" t="n">
-        <v>0.6498527472746318</v>
+        <v>0.6574485030909076</v>
       </c>
       <c r="S7" t="n">
-        <v>0.003895600075272372</v>
+        <v>0.00430853970919953</v>
       </c>
       <c r="T7" t="n">
-        <v>0.9821167883211679</v>
+        <v>0.9420113544201134</v>
       </c>
       <c r="U7" t="n">
-        <v>0.01484589266800504</v>
+        <v>0.0224173154275511</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>0.6453 ± 0.0059</t>
+          <t>0.6441 ± 0.0075</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.7821 ± 0.0045</t>
+          <t>0.7743 ± 0.0071</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.6499 ± 0.0039</t>
+          <t>0.6574 ± 0.0043</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>0.9821 ± 0.0148</t>
+          <t>0.9420 ± 0.0224</t>
         </is>
       </c>
       <c r="Z7" t="n">
-        <v>0.1807833859095689</v>
+        <v>0.1819400630914828</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.08782573374983682</v>
+        <v>0.09564102147348086</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.1943435054617062</v>
+        <v>0.1867477496454304</v>
       </c>
       <c r="AC7" t="n">
-        <v>-0.08467153284671536</v>
+        <v>-0.04456609894566088</v>
       </c>
       <c r="AD7" t="inlineStr">
         <is>
@@ -1892,60 +1904,60 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>0.5559674027339643</v>
+        <v>0.5680862250262881</v>
       </c>
       <c r="O8" t="n">
-        <v>0.01407357408562904</v>
+        <v>0.009487789237025089</v>
       </c>
       <c r="P8" t="n">
-        <v>0.6603305628827781</v>
+        <v>0.662978545924923</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.01126578902247099</v>
+        <v>0.007824515576590557</v>
       </c>
       <c r="R8" t="n">
-        <v>0.6549430158726766</v>
+        <v>0.6709258184989553</v>
       </c>
       <c r="S8" t="n">
-        <v>0.01058806418293841</v>
+        <v>0.009330971411173946</v>
       </c>
       <c r="T8" t="n">
-        <v>0.6658556366585564</v>
+        <v>0.655433901054339</v>
       </c>
       <c r="U8" t="n">
-        <v>0.01322749913244128</v>
+        <v>0.01338819930402441</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>0.5560 ± 0.0141</t>
+          <t>0.5681 ± 0.0095</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>0.6603 ± 0.0113</t>
+          <t>0.6630 ± 0.0078</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>0.6549 ± 0.0106</t>
+          <t>0.6709 ± 0.0093</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>0.6659 ± 0.0132</t>
+          <t>0.6554 ± 0.0134</t>
         </is>
       </c>
       <c r="Z8" t="n">
-        <v>0.2604626708727655</v>
+        <v>0.2483438485804417</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.1978076886129809</v>
+        <v>0.1951597055708361</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.2049145885005589</v>
+        <v>0.1889317858742802</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.1905920519059205</v>
+        <v>0.201013787510138</v>
       </c>
       <c r="AD8" t="inlineStr">
         <is>
@@ -2004,60 +2016,60 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>0.6484752891692954</v>
+        <v>0.6548895899053628</v>
       </c>
       <c r="O9" t="n">
-        <v>0.0005613605810741979</v>
+        <v>0.004497957638693293</v>
       </c>
       <c r="P9" t="n">
-        <v>0.7866897105966408</v>
+        <v>0.7896694319910493</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.0002824016647629441</v>
+        <v>0.002039360160543009</v>
       </c>
       <c r="R9" t="n">
-        <v>0.6484171357248467</v>
+        <v>0.6527431111348478</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0003542776151876643</v>
+        <v>0.003138397897206637</v>
       </c>
       <c r="T9" t="n">
-        <v>0.999918896999189</v>
+        <v>0.9993106244931063</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0002433090024331008</v>
+        <v>0.0009256052076653137</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>0.6485 ± 0.0006</t>
+          <t>0.6549 ± 0.0045</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>0.7867 ± 0.0003</t>
+          <t>0.7897 ± 0.0020</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>0.6484 ± 0.0004</t>
+          <t>0.6527 ± 0.0031</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>0.9999 ± 0.0002</t>
+          <t>0.9993 ± 0.0009</t>
         </is>
       </c>
       <c r="Z9" t="n">
-        <v>0.1424290220820189</v>
+        <v>0.1360147213459515</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.06097872233094215</v>
+        <v>0.05799900093653365</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.1547514702144538</v>
+        <v>0.1504254948044527</v>
       </c>
       <c r="AC9" t="n">
-        <v>-0.1025141930251419</v>
+        <v>-0.1019059205190591</v>
       </c>
       <c r="AD9" t="inlineStr">
         <is>
@@ -2116,60 +2128,60 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0.6484490010515247</v>
+        <v>0.6547318611987382</v>
       </c>
       <c r="O10" t="n">
-        <v>0.0004854412542749546</v>
+        <v>0.004834727206129407</v>
       </c>
       <c r="P10" t="n">
-        <v>0.7866703474864103</v>
+        <v>0.7895744661195588</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.0002290005449719912</v>
+        <v>0.002176516661522406</v>
       </c>
       <c r="R10" t="n">
-        <v>0.6484079012701597</v>
+        <v>0.6526670683359679</v>
       </c>
       <c r="S10" t="n">
-        <v>0.00032713558483582</v>
+        <v>0.003400314398859348</v>
       </c>
       <c r="T10" t="n">
-        <v>0.9998783454987834</v>
+        <v>0.9991889699918897</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0002596562951108327</v>
+        <v>0.001175294139999153</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>0.6484 ± 0.0005</t>
+          <t>0.6547 ± 0.0048</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>0.7867 ± 0.0002</t>
+          <t>0.7896 ± 0.0022</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>0.6484 ± 0.0003</t>
+          <t>0.6527 ± 0.0034</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>0.9999 ± 0.0003</t>
+          <t>0.9992 ± 0.0012</t>
         </is>
       </c>
       <c r="Z10" t="n">
-        <v>0.1407991587802315</v>
+        <v>0.1345162986330181</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.06022918994327531</v>
+        <v>0.05732507131012676</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.1519932360006231</v>
+        <v>0.1477340689348149</v>
       </c>
       <c r="AC10" t="n">
-        <v>-0.1007299270072993</v>
+        <v>-0.1000405515004056</v>
       </c>
       <c r="AD10" t="inlineStr">
         <is>
@@ -2228,60 +2240,60 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>0.6585699263932703</v>
+        <v>0.410173501577287</v>
       </c>
       <c r="O11" t="n">
-        <v>0.01199487378174651</v>
+        <v>0.1251307806228123</v>
       </c>
       <c r="P11" t="n">
-        <v>0.7909556912350302</v>
+        <v>0.3678103822357782</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.006560204671752298</v>
+        <v>0.2273457362929169</v>
       </c>
       <c r="R11" t="n">
-        <v>0.6558487825071249</v>
+        <v>0.5062172311485748</v>
       </c>
       <c r="S11" t="n">
-        <v>0.007518028486105992</v>
+        <v>0.1185081834044415</v>
       </c>
       <c r="T11" t="n">
-        <v>0.9962692619626925</v>
+        <v>0.3475669099756691</v>
       </c>
       <c r="U11" t="n">
-        <v>0.008536644668052942</v>
+        <v>0.3317138734611962</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>0.6586 ± 0.0120</t>
+          <t>0.4102 ± 0.1251</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>0.7910 ± 0.0066</t>
+          <t>0.3678 ± 0.2273</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>0.6558 ± 0.0075</t>
+          <t>0.5062 ± 0.1185</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>0.9963 ± 0.0085</t>
+          <t>0.3476 ± 0.3317</t>
         </is>
       </c>
       <c r="Z11" t="n">
-        <v>0.06716614090431117</v>
+        <v>0.3155625657202944</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.02152226100326138</v>
+        <v>0.4446675700025134</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.07382153816307357</v>
+        <v>0.2234530895216237</v>
       </c>
       <c r="AC11" t="n">
-        <v>-0.07976480129764796</v>
+        <v>0.5689375506893755</v>
       </c>
       <c r="AD11" t="inlineStr">
         <is>
@@ -2304,152 +2316,152 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Model</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Accuracy Mean_TRTR</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Accuracy Std_TRTR</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>F1 Mean_TRTR</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>F1 Std_TRTR</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Precision Mean_TRTR</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Precision Std_TRTR</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Recall Mean_TRTR</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Recall Std_TRTR</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Accuracy (Mean±Std)_TRTR</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>F1 (Mean±Std)_TRTR</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Precision (Mean±Std)_TRTR</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Recall (Mean±Std)_TRTR</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Accuracy Mean_TSTR</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Accuracy Std_TSTR</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>F1 Mean_TSTR</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>F1 Std_TSTR</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Precision Mean_TSTR</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Precision Std_TSTR</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Recall Mean_TSTR</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Recall Std_TSTR</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Accuracy (Mean±Std)_TSTR</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>F1 (Mean±Std)_TSTR</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Precision (Mean±Std)_TSTR</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Recall (Mean±Std)_TSTR</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>Accuracy_Drop</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>F1_Drop</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>Precision_Drop</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>Recall_Drop</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>Synthetic_Model</t>
         </is>
@@ -2842,60 +2854,60 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>0.8492639327024186</v>
+        <v>0.8491587802313354</v>
       </c>
       <c r="O5" t="n">
-        <v>0.008238043493988417</v>
+        <v>0.008191438239908467</v>
       </c>
       <c r="P5" t="n">
-        <v>0.8867625486960373</v>
+        <v>0.8866750511791677</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.006095869608256755</v>
+        <v>0.006052810530611546</v>
       </c>
       <c r="R5" t="n">
-        <v>0.8643581939924762</v>
+        <v>0.864337534401223</v>
       </c>
       <c r="S5" t="n">
-        <v>0.007845151158177936</v>
+        <v>0.00784290839772875</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9104217356042174</v>
+        <v>0.9102595296025953</v>
       </c>
       <c r="U5" t="n">
-        <v>0.008035850504221885</v>
+        <v>0.007927896113104536</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>0.8493 ± 0.0082</t>
+          <t>0.8492 ± 0.0082</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.8868 ± 0.0061</t>
+          <t>0.8867 ± 0.0061</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.8644 ± 0.0078</t>
+          <t>0.8643 ± 0.0078</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>0.9104 ± 0.0080</t>
+          <t>0.9103 ± 0.0079</t>
         </is>
       </c>
       <c r="Z5" t="n">
-        <v>0.02223974763406933</v>
+        <v>0.02234490010515255</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.01868401748698501</v>
+        <v>0.01877151500385466</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.001343624536752741</v>
+        <v>0.001364284128005933</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.03860502838605029</v>
+        <v>0.03876723438767238</v>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
@@ -3590,152 +3602,152 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Model</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Accuracy Mean_TRTR</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Accuracy Std_TRTR</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>F1 Mean_TRTR</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>F1 Std_TRTR</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Precision Mean_TRTR</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Precision Std_TRTR</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Recall Mean_TRTR</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Recall Std_TRTR</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Accuracy (Mean±Std)_TRTR</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>F1 (Mean±Std)_TRTR</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Precision (Mean±Std)_TRTR</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Recall (Mean±Std)_TRTR</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Accuracy Mean_TSTR</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Accuracy Std_TSTR</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>F1 Mean_TSTR</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>F1 Std_TSTR</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Precision Mean_TSTR</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Precision Std_TSTR</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Recall Mean_TSTR</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Recall Std_TSTR</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Accuracy (Mean±Std)_TSTR</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>F1 (Mean±Std)_TSTR</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Precision (Mean±Std)_TSTR</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Recall (Mean±Std)_TSTR</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>Accuracy_Drop</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>F1_Drop</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>Precision_Drop</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>Recall_Drop</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>Synthetic_Model</t>
         </is>
@@ -10848,60 +10860,60 @@
         </is>
       </c>
       <c r="N65" t="n">
-        <v>0.8492639327024186</v>
+        <v>0.8491587802313354</v>
       </c>
       <c r="O65" t="n">
-        <v>0.008238043493988417</v>
+        <v>0.008191438239908467</v>
       </c>
       <c r="P65" t="n">
-        <v>0.8867625486960373</v>
+        <v>0.8866750511791677</v>
       </c>
       <c r="Q65" t="n">
-        <v>0.006095869608256755</v>
+        <v>0.006052810530611546</v>
       </c>
       <c r="R65" t="n">
-        <v>0.8643581939924762</v>
+        <v>0.864337534401223</v>
       </c>
       <c r="S65" t="n">
-        <v>0.007845151158177936</v>
+        <v>0.00784290839772875</v>
       </c>
       <c r="T65" t="n">
-        <v>0.9104217356042174</v>
+        <v>0.9102595296025953</v>
       </c>
       <c r="U65" t="n">
-        <v>0.008035850504221885</v>
+        <v>0.007927896113104536</v>
       </c>
       <c r="V65" t="inlineStr">
         <is>
-          <t>0.8493 ± 0.0082</t>
+          <t>0.8492 ± 0.0082</t>
         </is>
       </c>
       <c r="W65" t="inlineStr">
         <is>
-          <t>0.8868 ± 0.0061</t>
+          <t>0.8867 ± 0.0061</t>
         </is>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>0.8644 ± 0.0078</t>
+          <t>0.8643 ± 0.0078</t>
         </is>
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>0.9104 ± 0.0080</t>
+          <t>0.9103 ± 0.0079</t>
         </is>
       </c>
       <c r="Z65" t="n">
-        <v>0.02223974763406933</v>
+        <v>0.02234490010515255</v>
       </c>
       <c r="AA65" t="n">
-        <v>0.01868401748698501</v>
+        <v>0.01877151500385466</v>
       </c>
       <c r="AB65" t="n">
-        <v>0.001343624536752741</v>
+        <v>0.001364284128005933</v>
       </c>
       <c r="AC65" t="n">
-        <v>0.03860502838605029</v>
+        <v>0.03876723438767238</v>
       </c>
       <c r="AD65" t="inlineStr">
         <is>
@@ -11632,60 +11644,60 @@
         </is>
       </c>
       <c r="N72" t="n">
-        <v>0.6348580441640378</v>
+        <v>0.6350157728706625</v>
       </c>
       <c r="O72" t="n">
-        <v>0.007403734637461534</v>
+        <v>0.01100728412878248</v>
       </c>
       <c r="P72" t="n">
-        <v>0.7667000074249125</v>
+        <v>0.7603254543816355</v>
       </c>
       <c r="Q72" t="n">
-        <v>0.005034609332349129</v>
+        <v>0.008034252722485523</v>
       </c>
       <c r="R72" t="n">
-        <v>0.6544041973465721</v>
+        <v>0.6619125822373438</v>
       </c>
       <c r="S72" t="n">
-        <v>0.004338417108145803</v>
+        <v>0.005858886471172387</v>
       </c>
       <c r="T72" t="n">
-        <v>0.9255879967558801</v>
+        <v>0.8931873479318735</v>
       </c>
       <c r="U72" t="n">
-        <v>0.009997815966181945</v>
+        <v>0.01386861313868614</v>
       </c>
       <c r="V72" t="inlineStr">
         <is>
-          <t>0.6349 ± 0.0074</t>
+          <t>0.6350 ± 0.0110</t>
         </is>
       </c>
       <c r="W72" t="inlineStr">
         <is>
-          <t>0.7667 ± 0.0050</t>
+          <t>0.7603 ± 0.0080</t>
         </is>
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>0.6544 ± 0.0043</t>
+          <t>0.6619 ± 0.0059</t>
         </is>
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>0.9256 ± 0.0100</t>
+          <t>0.8932 ± 0.0139</t>
         </is>
       </c>
       <c r="Z72" t="n">
-        <v>0.2454784437434279</v>
+        <v>0.2453207150368032</v>
       </c>
       <c r="AA72" t="n">
-        <v>0.1439488457518913</v>
+        <v>0.1503233987951683</v>
       </c>
       <c r="AB72" t="n">
-        <v>0.2280846643005098</v>
+        <v>0.220576279409738</v>
       </c>
       <c r="AC72" t="n">
-        <v>0.01508515815085143</v>
+        <v>0.04748580697485805</v>
       </c>
       <c r="AD72" t="inlineStr">
         <is>
@@ -11744,60 +11756,60 @@
         </is>
       </c>
       <c r="N73" t="n">
-        <v>0.6383280757097791</v>
+        <v>0.6346740273396425</v>
       </c>
       <c r="O73" t="n">
-        <v>0.0109225784870775</v>
+        <v>0.01333046061162599</v>
       </c>
       <c r="P73" t="n">
-        <v>0.7683501460435098</v>
+        <v>0.7597423295254266</v>
       </c>
       <c r="Q73" t="n">
-        <v>0.006850936582404506</v>
+        <v>0.008993136587323919</v>
       </c>
       <c r="R73" t="n">
-        <v>0.6569913439502555</v>
+        <v>0.6621770093572454</v>
       </c>
       <c r="S73" t="n">
-        <v>0.006793804218780486</v>
+        <v>0.007696943175684294</v>
       </c>
       <c r="T73" t="n">
-        <v>0.9252635847526356</v>
+        <v>0.8910786699107867</v>
       </c>
       <c r="U73" t="n">
-        <v>0.0112760153608929</v>
+        <v>0.01278781133215969</v>
       </c>
       <c r="V73" t="inlineStr">
         <is>
-          <t>0.6383 ± 0.0109</t>
+          <t>0.6347 ± 0.0133</t>
         </is>
       </c>
       <c r="W73" t="inlineStr">
         <is>
-          <t>0.7684 ± 0.0069</t>
+          <t>0.7597 ± 0.0090</t>
         </is>
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>0.6570 ± 0.0068</t>
+          <t>0.6622 ± 0.0077</t>
         </is>
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>0.9253 ± 0.0113</t>
+          <t>0.8911 ± 0.0128</t>
         </is>
       </c>
       <c r="Z73" t="n">
-        <v>0.2400105152471084</v>
+        <v>0.243664563617245</v>
       </c>
       <c r="AA73" t="n">
-        <v>0.1416865634162571</v>
+        <v>0.1502943799343402</v>
       </c>
       <c r="AB73" t="n">
-        <v>0.217012055597525</v>
+        <v>0.2118263901905351</v>
       </c>
       <c r="AC73" t="n">
-        <v>0.02392538523925403</v>
+        <v>0.05811030008110296</v>
       </c>
       <c r="AD73" t="inlineStr">
         <is>
@@ -11856,60 +11868,60 @@
         </is>
       </c>
       <c r="N74" t="n">
-        <v>0.6310988433228182</v>
+        <v>0.662565720294427</v>
       </c>
       <c r="O74" t="n">
-        <v>0.01057099444446813</v>
+        <v>0.0169301193155502</v>
       </c>
       <c r="P74" t="n">
-        <v>0.7517808777331801</v>
+        <v>0.7682960618487664</v>
       </c>
       <c r="Q74" t="n">
-        <v>0.008808504610388224</v>
+        <v>0.01267884580834273</v>
       </c>
       <c r="R74" t="n">
-        <v>0.6666927638610544</v>
+        <v>0.6922262985485927</v>
       </c>
       <c r="S74" t="n">
-        <v>0.0070720508501763</v>
+        <v>0.00974024592714598</v>
       </c>
       <c r="T74" t="n">
-        <v>0.8621654501216545</v>
+        <v>0.8633008921330088</v>
       </c>
       <c r="U74" t="n">
-        <v>0.02189289091961426</v>
+        <v>0.02004118167164525</v>
       </c>
       <c r="V74" t="inlineStr">
         <is>
-          <t>0.6311 ± 0.0106</t>
+          <t>0.6626 ± 0.0169</t>
         </is>
       </c>
       <c r="W74" t="inlineStr">
         <is>
-          <t>0.7518 ± 0.0088</t>
+          <t>0.7683 ± 0.0127</t>
         </is>
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>0.6667 ± 0.0071</t>
+          <t>0.6922 ± 0.0097</t>
         </is>
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>0.8622 ± 0.0219</t>
+          <t>0.8633 ± 0.0200</t>
         </is>
       </c>
       <c r="Z74" t="n">
-        <v>0.2468980021030491</v>
+        <v>0.2154311251314404</v>
       </c>
       <c r="AA74" t="n">
-        <v>0.1570949489768096</v>
+        <v>0.1405797648612234</v>
       </c>
       <c r="AB74" t="n">
-        <v>0.2143390609425785</v>
+        <v>0.1888055262550401</v>
       </c>
       <c r="AC74" t="n">
-        <v>0.07643957826439596</v>
+        <v>0.07530413625304166</v>
       </c>
       <c r="AD74" t="inlineStr">
         <is>
@@ -11968,60 +11980,60 @@
         </is>
       </c>
       <c r="N75" t="n">
-        <v>0.6281808622502629</v>
+        <v>0.629074658254469</v>
       </c>
       <c r="O75" t="n">
-        <v>0.008438608645194129</v>
+        <v>0.00972091799610684</v>
       </c>
       <c r="P75" t="n">
-        <v>0.7578194488136557</v>
+        <v>0.75329248607062</v>
       </c>
       <c r="Q75" t="n">
-        <v>0.005639916438486107</v>
+        <v>0.007593777351620037</v>
       </c>
       <c r="R75" t="n">
-        <v>0.6558601421759096</v>
+        <v>0.6621154684467924</v>
       </c>
       <c r="S75" t="n">
-        <v>0.005674490808419633</v>
+        <v>0.005626386807195845</v>
       </c>
       <c r="T75" t="n">
-        <v>0.8974452554744528</v>
+        <v>0.8737631792376318</v>
       </c>
       <c r="U75" t="n">
-        <v>0.01186774144616095</v>
+        <v>0.01600942216071113</v>
       </c>
       <c r="V75" t="inlineStr">
         <is>
-          <t>0.6282 ± 0.0084</t>
+          <t>0.6291 ± 0.0097</t>
         </is>
       </c>
       <c r="W75" t="inlineStr">
         <is>
-          <t>0.7578 ± 0.0056</t>
+          <t>0.7533 ± 0.0076</t>
         </is>
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>0.6559 ± 0.0057</t>
+          <t>0.6621 ± 0.0056</t>
         </is>
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>0.8974 ± 0.0119</t>
+          <t>0.8738 ± 0.0160</t>
         </is>
       </c>
       <c r="Z75" t="n">
-        <v>0.243322818086225</v>
+        <v>0.242429022082019</v>
       </c>
       <c r="AA75" t="n">
-        <v>0.1476271173693666</v>
+        <v>0.1521540801124023</v>
       </c>
       <c r="AB75" t="n">
-        <v>0.2098416763533193</v>
+        <v>0.2035863500824365</v>
       </c>
       <c r="AC75" t="n">
-        <v>0.05158150851581489</v>
+        <v>0.07526358475263584</v>
       </c>
       <c r="AD75" t="inlineStr">
         <is>
@@ -12080,60 +12092,60 @@
         </is>
       </c>
       <c r="N76" t="n">
-        <v>0.6043638275499473</v>
+        <v>0.6023396424815983</v>
       </c>
       <c r="O76" t="n">
-        <v>0.01003297302396089</v>
+        <v>0.01224306820402052</v>
       </c>
       <c r="P76" t="n">
-        <v>0.724332197313248</v>
+        <v>0.7153860210376379</v>
       </c>
       <c r="Q76" t="n">
-        <v>0.007641871099014639</v>
+        <v>0.009801680407231356</v>
       </c>
       <c r="R76" t="n">
-        <v>0.660512122828971</v>
+        <v>0.667250789080277</v>
       </c>
       <c r="S76" t="n">
-        <v>0.006529411639070338</v>
+        <v>0.007553444844003219</v>
       </c>
       <c r="T76" t="n">
-        <v>0.8019059205190592</v>
+        <v>0.7710867802108679</v>
       </c>
       <c r="U76" t="n">
-        <v>0.01278401727314183</v>
+        <v>0.01463819297059818</v>
       </c>
       <c r="V76" t="inlineStr">
         <is>
-          <t>0.6044 ± 0.0100</t>
+          <t>0.6023 ± 0.0122</t>
         </is>
       </c>
       <c r="W76" t="inlineStr">
         <is>
-          <t>0.7243 ± 0.0076</t>
+          <t>0.7154 ± 0.0098</t>
         </is>
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>0.6605 ± 0.0065</t>
+          <t>0.6673 ± 0.0076</t>
         </is>
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>0.8019 ± 0.0128</t>
+          <t>0.7711 ± 0.0146</t>
         </is>
       </c>
       <c r="Z76" t="n">
-        <v>0.2335436382754995</v>
+        <v>0.2355678233438485</v>
       </c>
       <c r="AA76" t="n">
-        <v>0.1582919445598115</v>
+        <v>0.1672381208354217</v>
       </c>
       <c r="AB76" t="n">
-        <v>0.1712654339740611</v>
+        <v>0.1645267677227551</v>
       </c>
       <c r="AC76" t="n">
-        <v>0.1381995133819952</v>
+        <v>0.1690186536901865</v>
       </c>
       <c r="AD76" t="inlineStr">
         <is>
@@ -12192,60 +12204,60 @@
         </is>
       </c>
       <c r="N77" t="n">
-        <v>0.6452944269190326</v>
+        <v>0.6441377497371187</v>
       </c>
       <c r="O77" t="n">
-        <v>0.005906408310205905</v>
+        <v>0.007461427371196214</v>
       </c>
       <c r="P77" t="n">
-        <v>0.7820984572517805</v>
+        <v>0.7742831695281365</v>
       </c>
       <c r="Q77" t="n">
-        <v>0.004544786967065663</v>
+        <v>0.007054059690694768</v>
       </c>
       <c r="R77" t="n">
-        <v>0.6498527472746318</v>
+        <v>0.6574485030909076</v>
       </c>
       <c r="S77" t="n">
-        <v>0.003895600075272372</v>
+        <v>0.00430853970919953</v>
       </c>
       <c r="T77" t="n">
-        <v>0.9821167883211679</v>
+        <v>0.9420113544201134</v>
       </c>
       <c r="U77" t="n">
-        <v>0.01484589266800504</v>
+        <v>0.0224173154275511</v>
       </c>
       <c r="V77" t="inlineStr">
         <is>
-          <t>0.6453 ± 0.0059</t>
+          <t>0.6441 ± 0.0075</t>
         </is>
       </c>
       <c r="W77" t="inlineStr">
         <is>
-          <t>0.7821 ± 0.0045</t>
+          <t>0.7743 ± 0.0071</t>
         </is>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>0.6499 ± 0.0039</t>
+          <t>0.6574 ± 0.0043</t>
         </is>
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>0.9821 ± 0.0148</t>
+          <t>0.9420 ± 0.0224</t>
         </is>
       </c>
       <c r="Z77" t="n">
-        <v>0.1807833859095689</v>
+        <v>0.1819400630914828</v>
       </c>
       <c r="AA77" t="n">
-        <v>0.08782573374983682</v>
+        <v>0.09564102147348086</v>
       </c>
       <c r="AB77" t="n">
-        <v>0.1943435054617062</v>
+        <v>0.1867477496454304</v>
       </c>
       <c r="AC77" t="n">
-        <v>-0.08467153284671536</v>
+        <v>-0.04456609894566088</v>
       </c>
       <c r="AD77" t="inlineStr">
         <is>
@@ -12304,60 +12316,60 @@
         </is>
       </c>
       <c r="N78" t="n">
-        <v>0.5559674027339643</v>
+        <v>0.5680862250262881</v>
       </c>
       <c r="O78" t="n">
-        <v>0.01407357408562904</v>
+        <v>0.009487789237025089</v>
       </c>
       <c r="P78" t="n">
-        <v>0.6603305628827781</v>
+        <v>0.662978545924923</v>
       </c>
       <c r="Q78" t="n">
-        <v>0.01126578902247099</v>
+        <v>0.007824515576590557</v>
       </c>
       <c r="R78" t="n">
-        <v>0.6549430158726766</v>
+        <v>0.6709258184989553</v>
       </c>
       <c r="S78" t="n">
-        <v>0.01058806418293841</v>
+        <v>0.009330971411173946</v>
       </c>
       <c r="T78" t="n">
-        <v>0.6658556366585564</v>
+        <v>0.655433901054339</v>
       </c>
       <c r="U78" t="n">
-        <v>0.01322749913244128</v>
+        <v>0.01338819930402441</v>
       </c>
       <c r="V78" t="inlineStr">
         <is>
-          <t>0.5560 ± 0.0141</t>
+          <t>0.5681 ± 0.0095</t>
         </is>
       </c>
       <c r="W78" t="inlineStr">
         <is>
-          <t>0.6603 ± 0.0113</t>
+          <t>0.6630 ± 0.0078</t>
         </is>
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>0.6549 ± 0.0106</t>
+          <t>0.6709 ± 0.0093</t>
         </is>
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>0.6659 ± 0.0132</t>
+          <t>0.6554 ± 0.0134</t>
         </is>
       </c>
       <c r="Z78" t="n">
-        <v>0.2604626708727655</v>
+        <v>0.2483438485804417</v>
       </c>
       <c r="AA78" t="n">
-        <v>0.1978076886129809</v>
+        <v>0.1951597055708361</v>
       </c>
       <c r="AB78" t="n">
-        <v>0.2049145885005589</v>
+        <v>0.1889317858742802</v>
       </c>
       <c r="AC78" t="n">
-        <v>0.1905920519059205</v>
+        <v>0.201013787510138</v>
       </c>
       <c r="AD78" t="inlineStr">
         <is>
@@ -12416,60 +12428,60 @@
         </is>
       </c>
       <c r="N79" t="n">
-        <v>0.6484752891692954</v>
+        <v>0.6548895899053628</v>
       </c>
       <c r="O79" t="n">
-        <v>0.0005613605810741979</v>
+        <v>0.004497957638693293</v>
       </c>
       <c r="P79" t="n">
-        <v>0.7866897105966408</v>
+        <v>0.7896694319910493</v>
       </c>
       <c r="Q79" t="n">
-        <v>0.0002824016647629441</v>
+        <v>0.002039360160543009</v>
       </c>
       <c r="R79" t="n">
-        <v>0.6484171357248467</v>
+        <v>0.6527431111348478</v>
       </c>
       <c r="S79" t="n">
-        <v>0.0003542776151876643</v>
+        <v>0.003138397897206637</v>
       </c>
       <c r="T79" t="n">
-        <v>0.999918896999189</v>
+        <v>0.9993106244931063</v>
       </c>
       <c r="U79" t="n">
-        <v>0.0002433090024331008</v>
+        <v>0.0009256052076653137</v>
       </c>
       <c r="V79" t="inlineStr">
         <is>
-          <t>0.6485 ± 0.0006</t>
+          <t>0.6549 ± 0.0045</t>
         </is>
       </c>
       <c r="W79" t="inlineStr">
         <is>
-          <t>0.7867 ± 0.0003</t>
+          <t>0.7897 ± 0.0020</t>
         </is>
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>0.6484 ± 0.0004</t>
+          <t>0.6527 ± 0.0031</t>
         </is>
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>0.9999 ± 0.0002</t>
+          <t>0.9993 ± 0.0009</t>
         </is>
       </c>
       <c r="Z79" t="n">
-        <v>0.1424290220820189</v>
+        <v>0.1360147213459515</v>
       </c>
       <c r="AA79" t="n">
-        <v>0.06097872233094215</v>
+        <v>0.05799900093653365</v>
       </c>
       <c r="AB79" t="n">
-        <v>0.1547514702144538</v>
+        <v>0.1504254948044527</v>
       </c>
       <c r="AC79" t="n">
-        <v>-0.1025141930251419</v>
+        <v>-0.1019059205190591</v>
       </c>
       <c r="AD79" t="inlineStr">
         <is>
@@ -12528,60 +12540,60 @@
         </is>
       </c>
       <c r="N80" t="n">
-        <v>0.6484490010515247</v>
+        <v>0.6547318611987382</v>
       </c>
       <c r="O80" t="n">
-        <v>0.0004854412542749546</v>
+        <v>0.004834727206129407</v>
       </c>
       <c r="P80" t="n">
-        <v>0.7866703474864103</v>
+        <v>0.7895744661195588</v>
       </c>
       <c r="Q80" t="n">
-        <v>0.0002290005449719912</v>
+        <v>0.002176516661522406</v>
       </c>
       <c r="R80" t="n">
-        <v>0.6484079012701597</v>
+        <v>0.6526670683359679</v>
       </c>
       <c r="S80" t="n">
-        <v>0.00032713558483582</v>
+        <v>0.003400314398859348</v>
       </c>
       <c r="T80" t="n">
-        <v>0.9998783454987834</v>
+        <v>0.9991889699918897</v>
       </c>
       <c r="U80" t="n">
-        <v>0.0002596562951108327</v>
+        <v>0.001175294139999153</v>
       </c>
       <c r="V80" t="inlineStr">
         <is>
-          <t>0.6484 ± 0.0005</t>
+          <t>0.6547 ± 0.0048</t>
         </is>
       </c>
       <c r="W80" t="inlineStr">
         <is>
-          <t>0.7867 ± 0.0002</t>
+          <t>0.7896 ± 0.0022</t>
         </is>
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>0.6484 ± 0.0003</t>
+          <t>0.6527 ± 0.0034</t>
         </is>
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>0.9999 ± 0.0003</t>
+          <t>0.9992 ± 0.0012</t>
         </is>
       </c>
       <c r="Z80" t="n">
-        <v>0.1407991587802315</v>
+        <v>0.1345162986330181</v>
       </c>
       <c r="AA80" t="n">
-        <v>0.06022918994327531</v>
+        <v>0.05732507131012676</v>
       </c>
       <c r="AB80" t="n">
-        <v>0.1519932360006231</v>
+        <v>0.1477340689348149</v>
       </c>
       <c r="AC80" t="n">
-        <v>-0.1007299270072993</v>
+        <v>-0.1000405515004056</v>
       </c>
       <c r="AD80" t="inlineStr">
         <is>
@@ -12640,60 +12652,60 @@
         </is>
       </c>
       <c r="N81" t="n">
-        <v>0.6585699263932703</v>
+        <v>0.410173501577287</v>
       </c>
       <c r="O81" t="n">
-        <v>0.01199487378174651</v>
+        <v>0.1251307806228123</v>
       </c>
       <c r="P81" t="n">
-        <v>0.7909556912350302</v>
+        <v>0.3678103822357782</v>
       </c>
       <c r="Q81" t="n">
-        <v>0.006560204671752298</v>
+        <v>0.2273457362929169</v>
       </c>
       <c r="R81" t="n">
-        <v>0.6558487825071249</v>
+        <v>0.5062172311485748</v>
       </c>
       <c r="S81" t="n">
-        <v>0.007518028486105992</v>
+        <v>0.1185081834044415</v>
       </c>
       <c r="T81" t="n">
-        <v>0.9962692619626925</v>
+        <v>0.3475669099756691</v>
       </c>
       <c r="U81" t="n">
-        <v>0.008536644668052942</v>
+        <v>0.3317138734611962</v>
       </c>
       <c r="V81" t="inlineStr">
         <is>
-          <t>0.6586 ± 0.0120</t>
+          <t>0.4102 ± 0.1251</t>
         </is>
       </c>
       <c r="W81" t="inlineStr">
         <is>
-          <t>0.7910 ± 0.0066</t>
+          <t>0.3678 ± 0.2273</t>
         </is>
       </c>
       <c r="X81" t="inlineStr">
         <is>
-          <t>0.6558 ± 0.0075</t>
+          <t>0.5062 ± 0.1185</t>
         </is>
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>0.9963 ± 0.0085</t>
+          <t>0.3476 ± 0.3317</t>
         </is>
       </c>
       <c r="Z81" t="n">
-        <v>0.06716614090431117</v>
+        <v>0.3155625657202944</v>
       </c>
       <c r="AA81" t="n">
-        <v>0.02152226100326138</v>
+        <v>0.4446675700025134</v>
       </c>
       <c r="AB81" t="n">
-        <v>0.07382153816307357</v>
+        <v>0.2234530895216237</v>
       </c>
       <c r="AC81" t="n">
-        <v>-0.07976480129764796</v>
+        <v>0.5689375506893755</v>
       </c>
       <c r="AD81" t="inlineStr">
         <is>
@@ -12716,27 +12728,27 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Synthetic_Model</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Accuracy_Drop</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>F1_Drop</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Precision_Drop</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Recall_Drop</t>
         </is>
@@ -12863,16 +12875,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01993953732912719</v>
+        <v>0.01995005257623551</v>
       </c>
       <c r="C8" t="n">
-        <v>0.01598071969731233</v>
+        <v>0.0159894694489993</v>
       </c>
       <c r="D8" t="n">
-        <v>0.008963453724926329</v>
+        <v>0.008965519684051649</v>
       </c>
       <c r="E8" t="n">
-        <v>0.02376317923763178</v>
+        <v>0.02377939983779399</v>
       </c>
     </row>
     <row r="9">
@@ -12882,16 +12894,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.2000893796004206</v>
+        <v>0.2198790746582545</v>
       </c>
       <c r="C9" t="n">
-        <v>0.1177013015714433</v>
+        <v>0.1611382113832047</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1820367229508409</v>
+        <v>0.1886613502441107</v>
       </c>
       <c r="E9" t="n">
-        <v>0.01281427412814276</v>
+        <v>0.09486212489862129</v>
       </c>
     </row>
   </sheetData>
@@ -12909,152 +12921,152 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Model</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Accuracy Mean_TRTR</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Accuracy Std_TRTR</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>F1 Mean_TRTR</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>F1 Std_TRTR</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Precision Mean_TRTR</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Precision Std_TRTR</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Recall Mean_TRTR</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Recall Std_TRTR</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Accuracy (Mean±Std)_TRTR</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>F1 (Mean±Std)_TRTR</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Precision (Mean±Std)_TRTR</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Recall (Mean±Std)_TRTR</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Accuracy Mean_TSTR</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Accuracy Std_TSTR</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>F1 Mean_TSTR</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>F1 Std_TSTR</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Precision Mean_TSTR</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Precision Std_TSTR</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Recall Mean_TSTR</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Recall Std_TSTR</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Accuracy (Mean±Std)_TSTR</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>F1 (Mean±Std)_TSTR</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Precision (Mean±Std)_TSTR</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Recall (Mean±Std)_TSTR</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>Accuracy_Drop</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>F1_Drop</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>Precision_Drop</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>Recall_Drop</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>Synthetic_Model</t>
         </is>
@@ -14195,152 +14207,152 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Model</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Accuracy Mean_TRTR</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Accuracy Std_TRTR</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>F1 Mean_TRTR</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>F1 Std_TRTR</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Precision Mean_TRTR</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Precision Std_TRTR</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Recall Mean_TRTR</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Recall Std_TRTR</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Accuracy (Mean±Std)_TRTR</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>F1 (Mean±Std)_TRTR</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Precision (Mean±Std)_TRTR</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Recall (Mean±Std)_TRTR</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Accuracy Mean_TSTR</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Accuracy Std_TSTR</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>F1 Mean_TSTR</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>F1 Std_TSTR</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Precision Mean_TSTR</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Precision Std_TSTR</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Recall Mean_TSTR</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Recall Std_TSTR</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Accuracy (Mean±Std)_TSTR</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>F1 (Mean±Std)_TSTR</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Precision (Mean±Std)_TSTR</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Recall (Mean±Std)_TSTR</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>Accuracy_Drop</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>F1_Drop</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>Precision_Drop</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>Recall_Drop</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>Synthetic_Model</t>
         </is>
@@ -15481,152 +15493,152 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Model</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Accuracy Mean_TRTR</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Accuracy Std_TRTR</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>F1 Mean_TRTR</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>F1 Std_TRTR</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Precision Mean_TRTR</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Precision Std_TRTR</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Recall Mean_TRTR</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Recall Std_TRTR</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Accuracy (Mean±Std)_TRTR</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>F1 (Mean±Std)_TRTR</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Precision (Mean±Std)_TRTR</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Recall (Mean±Std)_TRTR</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Accuracy Mean_TSTR</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Accuracy Std_TSTR</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>F1 Mean_TSTR</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>F1 Std_TSTR</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Precision Mean_TSTR</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Precision Std_TSTR</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Recall Mean_TSTR</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Recall Std_TSTR</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Accuracy (Mean±Std)_TSTR</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>F1 (Mean±Std)_TSTR</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Precision (Mean±Std)_TSTR</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Recall (Mean±Std)_TSTR</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>Accuracy_Drop</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>F1_Drop</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>Precision_Drop</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>Recall_Drop</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>Synthetic_Model</t>
         </is>
@@ -16767,152 +16779,152 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Model</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Accuracy Mean_TRTR</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Accuracy Std_TRTR</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>F1 Mean_TRTR</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>F1 Std_TRTR</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Precision Mean_TRTR</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Precision Std_TRTR</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Recall Mean_TRTR</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Recall Std_TRTR</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Accuracy (Mean±Std)_TRTR</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>F1 (Mean±Std)_TRTR</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Precision (Mean±Std)_TRTR</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Recall (Mean±Std)_TRTR</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Accuracy Mean_TSTR</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Accuracy Std_TSTR</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>F1 Mean_TSTR</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>F1 Std_TSTR</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Precision Mean_TSTR</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Precision Std_TSTR</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Recall Mean_TSTR</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Recall Std_TSTR</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Accuracy (Mean±Std)_TSTR</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>F1 (Mean±Std)_TSTR</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Precision (Mean±Std)_TSTR</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Recall (Mean±Std)_TSTR</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>Accuracy_Drop</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>F1_Drop</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>Precision_Drop</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>Recall_Drop</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>Synthetic_Model</t>
         </is>
@@ -18053,152 +18065,152 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Model</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Accuracy Mean_TRTR</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Accuracy Std_TRTR</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>F1 Mean_TRTR</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>F1 Std_TRTR</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Precision Mean_TRTR</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Precision Std_TRTR</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Recall Mean_TRTR</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Recall Std_TRTR</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Accuracy (Mean±Std)_TRTR</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>F1 (Mean±Std)_TRTR</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Precision (Mean±Std)_TRTR</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Recall (Mean±Std)_TRTR</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Accuracy Mean_TSTR</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Accuracy Std_TSTR</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>F1 Mean_TSTR</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>F1 Std_TSTR</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Precision Mean_TSTR</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Precision Std_TSTR</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Recall Mean_TSTR</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Recall Std_TSTR</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Accuracy (Mean±Std)_TSTR</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>F1 (Mean±Std)_TSTR</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Precision (Mean±Std)_TSTR</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Recall (Mean±Std)_TSTR</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>Accuracy_Drop</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>F1_Drop</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>Precision_Drop</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>Recall_Drop</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>Synthetic_Model</t>
         </is>
@@ -19339,152 +19351,152 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Model</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Accuracy Mean_TRTR</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Accuracy Std_TRTR</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>F1 Mean_TRTR</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>F1 Std_TRTR</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Precision Mean_TRTR</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Precision Std_TRTR</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Recall Mean_TRTR</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Recall Std_TRTR</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Accuracy (Mean±Std)_TRTR</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>F1 (Mean±Std)_TRTR</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Precision (Mean±Std)_TRTR</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Recall (Mean±Std)_TRTR</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Accuracy Mean_TSTR</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Accuracy Std_TSTR</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>F1 Mean_TSTR</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>F1 Std_TSTR</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Precision Mean_TSTR</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Precision Std_TSTR</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Recall Mean_TSTR</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Recall Std_TSTR</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Accuracy (Mean±Std)_TSTR</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>F1 (Mean±Std)_TSTR</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Precision (Mean±Std)_TSTR</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Recall (Mean±Std)_TSTR</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>Accuracy_Drop</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>F1_Drop</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>Precision_Drop</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>Recall_Drop</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>Synthetic_Model</t>
         </is>
